--- a/Results/Phase 2/Methanol/methanol resource use mineral and metals results.xlsx
+++ b/Results/Phase 2/Methanol/methanol resource use mineral and metals results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.575204143976725e-06</v>
+        <v>2.391056926956536e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.620782344548374e-06</v>
+        <v>2.445831478828332e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.553643102816893e-06</v>
+        <v>2.37916150794489e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.32856076307644e-06</v>
+        <v>2.290055964881207e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.558503660388911e-06</v>
+        <v>2.378734438049651e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.597299149956663e-06</v>
+        <v>2.408761004636161e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.573504039073904e-06</v>
+        <v>2.385863653073197e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.561581950421914e-06</v>
+        <v>2.38307471243346e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.581316641449605e-06</v>
+        <v>2.397940000339783e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.573637891503422e-06</v>
+        <v>2.391264825861061e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.55734297687011e-06</v>
+        <v>2.38466590476359e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.601555247402609e-06</v>
+        <v>2.402375382415053e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.563599823897249e-06</v>
+        <v>2.385765228708235e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.150442708497702e-06</v>
+        <v>3.954446976751559e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.562854257504415e-06</v>
+        <v>2.389960172525926e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.56032829058043e-06</v>
+        <v>2.383000140216641e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.554017047549035e-06</v>
+        <v>2.377906332282442e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.574912255892014e-06</v>
+        <v>2.392756371168952e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.559230781829324e-06</v>
+        <v>2.382174103325331e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.10984537286756e-06</v>
+        <v>2.920326525628898e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.594186300459498e-06</v>
+        <v>2.399215546936458e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.185998344507661e-06</v>
+        <v>2.992275696095704e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.573670342524887e-06</v>
+        <v>2.389859373435503e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.592446986591346e-06</v>
+        <v>2.40125449155073e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.922815827471659e-06</v>
+        <v>2.743698313039403e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.568430963679796e-06</v>
+        <v>2.390320625762985e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.618952465148226e-06</v>
+        <v>2.409815924637321e-06</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.696297012448462e-06</v>
+        <v>2.475799162712996e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.743383297836848e-06</v>
+        <v>2.519742329092905e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.784425373187037e-06</v>
+        <v>2.514985960253538e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.441639655898278e-06</v>
+        <v>2.351982267898415e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.668763937453891e-06</v>
+        <v>2.449879104752012e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.807189832014505e-06</v>
+        <v>2.532793193921363e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.729041246771656e-06</v>
+        <v>2.48474018889391e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.756404890577976e-06</v>
+        <v>2.503622640591774e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.743912464055294e-06</v>
+        <v>2.496458596523017e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.737767276455066e-06</v>
+        <v>2.472055372188164e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.714076284487697e-06</v>
+        <v>2.471072783093473e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.814238675160189e-06</v>
+        <v>2.528529819785161e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.658718992770365e-06</v>
+        <v>2.456677626535874e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.327162692603127e-06</v>
+        <v>4.112304053667649e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.646439321895884e-06</v>
+        <v>2.442744329024881e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.696698482253282e-06</v>
+        <v>2.468848629054546e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.718685736277445e-06</v>
+        <v>2.484286952491922e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.687621376384996e-06</v>
+        <v>2.465138042805212e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.6981361276329e-06</v>
+        <v>2.474327809383616e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.293140040057276e-06</v>
+        <v>3.048980637411049e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.731430952170659e-06</v>
+        <v>2.486524922008974e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.468831673355305e-06</v>
+        <v>3.203612273391203e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.67145256717237e-06</v>
+        <v>2.451802046955457e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.743036162893291e-06</v>
+        <v>2.50751150215778e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.090148318988515e-06</v>
+        <v>2.858051476081202e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.716096852480751e-06</v>
+        <v>2.492007740165473e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.793068317793765e-06</v>
+        <v>2.522116348933007e-06</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.593350478934112e-06</v>
+        <v>2.402300391708602e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.649260266744867e-06</v>
+        <v>2.457450512476056e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.609920560951604e-06</v>
+        <v>2.413303123531954e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.338351898590547e-06</v>
+        <v>2.296109393921817e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.579337757709845e-06</v>
+        <v>2.3889431899873e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.618361689227796e-06</v>
+        <v>2.420401106272458e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.587387117657083e-06</v>
+        <v>2.394149467069849e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.573488112100567e-06</v>
+        <v>2.391366964063761e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.60146959608914e-06</v>
+        <v>2.408802941948079e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.630438390227848e-06</v>
+        <v>2.4090284052728e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.575620811422331e-06</v>
+        <v>2.396888010200411e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.613576143626493e-06</v>
+        <v>2.409471603720257e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.588844164505512e-06</v>
+        <v>2.40197290250612e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.171553774268383e-06</v>
+        <v>3.974314622806821e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.568547341213984e-06</v>
+        <v>2.394117833748026e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.588283784829309e-06</v>
+        <v>2.400014449635827e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.597309448749097e-06</v>
+        <v>2.404258647286846e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.59413826420315e-06</v>
+        <v>2.404108618096686e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.596304927238553e-06</v>
+        <v>2.40369786219244e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.128073711257639e-06</v>
+        <v>2.934222634134871e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.617292257994926e-06</v>
+        <v>2.40544264723006e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.210418789517384e-06</v>
+        <v>3.011060247427974e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.599994065287963e-06</v>
+        <v>2.405826575038048e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.610210401396103e-06</v>
+        <v>2.410477559100357e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.94482564492365e-06</v>
+        <v>2.758545861732723e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.594049884667687e-06</v>
+        <v>2.404698742357998e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.635733678996951e-06</v>
+        <v>2.420979206970017e-06</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.613973715179081e-06</v>
+        <v>2.421911754803413e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.699225510010092e-06</v>
+        <v>2.48462471375856e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.653099168798411e-06</v>
+        <v>2.440065483857022e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.369382250541301e-06</v>
+        <v>2.318212732928441e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.604547987056821e-06</v>
+        <v>2.405531980067138e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.645046149435768e-06</v>
+        <v>2.436363428224021e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.60932290731677e-06</v>
+        <v>2.412461821378045e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.639128106970413e-06</v>
+        <v>2.432338060668712e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.631252396131549e-06</v>
+        <v>2.427344465353013e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.702125886941156e-06</v>
+        <v>2.44569313583276e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.603961744956026e-06</v>
+        <v>2.416295304473491e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.642705028602961e-06</v>
+        <v>2.430797143560313e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.607051860218865e-06</v>
+        <v>2.416807851233226e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.226017863416533e-06</v>
+        <v>4.025306389805397e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.58518922769282e-06</v>
+        <v>2.405183495280319e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.612970098206763e-06</v>
+        <v>2.415546618419379e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.61315118813577e-06</v>
+        <v>2.417359071179033e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.622788120352142e-06</v>
+        <v>2.423851216596298e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.623950474112553e-06</v>
+        <v>2.424304639782191e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.170100990097012e-06</v>
+        <v>2.971249670629072e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.644954609437766e-06</v>
+        <v>2.423137468087164e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.279539339551115e-06</v>
+        <v>3.068882810343439e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.619256940991886e-06</v>
+        <v>2.420254228199557e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.609763994777046e-06</v>
+        <v>2.414808038107045e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.010246721650193e-06</v>
+        <v>2.798474508319808e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.623706178644374e-06</v>
+        <v>2.426823111709561e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.657023798242327e-06</v>
+        <v>2.437655873466541e-06</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.634716178248458e-06</v>
+        <v>2.430996560995449e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.710861882738247e-06</v>
+        <v>2.492959225198401e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.715560453990757e-06</v>
+        <v>2.469794921261403e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.407359423790465e-06</v>
+        <v>2.329316359953778e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.61793717419899e-06</v>
+        <v>2.414661673747763e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.678706626564824e-06</v>
+        <v>2.451217555872156e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.629529742840841e-06</v>
+        <v>2.427248235245104e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.671084712195568e-06</v>
+        <v>2.449087546755479e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.65758671492604e-06</v>
+        <v>2.439789364538519e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.700453617460393e-06</v>
+        <v>2.447621354054516e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.62780304524289e-06</v>
+        <v>2.423442276527087e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.678894690074666e-06</v>
+        <v>2.444631812080253e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.610036880913386e-06</v>
+        <v>2.421274878909331e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.265336289604524e-06</v>
+        <v>4.060173835046885e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.613647622260995e-06</v>
+        <v>2.417410262093261e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.623214244246383e-06</v>
+        <v>2.420625362858704e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.622685295614195e-06</v>
+        <v>2.425245719005053e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.63030684932561e-06</v>
+        <v>2.428575075928867e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.643458756685622e-06</v>
+        <v>2.438325927187933e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.211967817189067e-06</v>
+        <v>2.996376243946232e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.667047119208493e-06</v>
+        <v>2.437149319018977e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.330265265675652e-06</v>
+        <v>3.108454191568019e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.635661179416832e-06</v>
+        <v>2.427410125334589e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.61783323322241e-06</v>
+        <v>2.426722348936242e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.04654085756938e-06</v>
+        <v>2.818338211806018e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.6503056754697e-06</v>
+        <v>2.446253357703586e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.68054761900575e-06</v>
+        <v>2.45184861898635e-06</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.643873159053236e-06</v>
+        <v>2.434219408881358e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.668158542063919e-06</v>
+        <v>2.47199441266791e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.704390064356226e-06</v>
+        <v>2.46793981094369e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.347215933687149e-06</v>
+        <v>2.30360635122237e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.606658242469095e-06</v>
+        <v>2.405063716608793e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.70136601717579e-06</v>
+        <v>2.450706975925596e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.655091311432345e-06</v>
+        <v>2.435390037533692e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.600649014665023e-06</v>
+        <v>2.40722141985297e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.653988391598453e-06</v>
+        <v>2.430719531771192e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.67190024981093e-06</v>
+        <v>2.429101505388746e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.681971657130601e-06</v>
+        <v>2.434741957578759e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.682100593834419e-06</v>
+        <v>2.428724812829377e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.614206131529697e-06</v>
+        <v>2.416060018077622e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.209293729276423e-06</v>
+        <v>4.004015231850956e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.586592542965232e-06</v>
+        <v>2.405798984607976e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.632984797100816e-06</v>
+        <v>2.4230593942941e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.628074510601659e-06</v>
+        <v>2.425329719419519e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.659903132917311e-06</v>
+        <v>2.425843369029272e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.643519512418707e-06</v>
+        <v>2.421509965753143e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.159013837666627e-06</v>
+        <v>2.953987394672095e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.641410376179563e-06</v>
+        <v>2.422118786178436e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.251679379637089e-06</v>
+        <v>3.044325755403352e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.620137758282021e-06</v>
+        <v>2.419148857495548e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.622951346068461e-06</v>
+        <v>2.420633651320877e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.003955137429474e-06</v>
+        <v>2.791759466260496e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.610089038589233e-06</v>
+        <v>2.417103666322309e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.659349094746112e-06</v>
+        <v>2.432792146414458e-06</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.687632048729296e-06</v>
+        <v>2.471298966499103e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.734472317978723e-06</v>
+        <v>2.512439552016349e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.79425454757403e-06</v>
+        <v>2.515099478465325e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.415892302176895e-06</v>
+        <v>2.349333892189092e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.666340740056667e-06</v>
+        <v>2.444420646793304e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.780569605469851e-06</v>
+        <v>2.501122727943278e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.715187322430385e-06</v>
+        <v>2.474603111750694e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.742044275443082e-06</v>
+        <v>2.49075720137374e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.733210392572047e-06</v>
+        <v>2.479913328929249e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.814238352968926e-06</v>
+        <v>2.517898222924323e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.825517390256285e-06</v>
+        <v>2.511875239479854e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.828755709374742e-06</v>
+        <v>2.511497432737491e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.664032096707654e-06</v>
+        <v>2.450845698426375e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.292739521651211e-06</v>
+        <v>4.081887828302591e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.630872434254853e-06</v>
+        <v>2.436384620452204e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.712450595238293e-06</v>
+        <v>2.468049051042766e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.715638108378867e-06</v>
+        <v>2.476380878439605e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.704342162023217e-06</v>
+        <v>2.46313897868446e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.713078229577098e-06</v>
+        <v>2.464582802655491e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.29969894400988e-06</v>
+        <v>3.03446163411622e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.709997959588444e-06</v>
+        <v>2.466058830716652e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.379889156154829e-06</v>
+        <v>3.130554332298235e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.665201739979885e-06</v>
+        <v>2.444156342935549e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.696147583941894e-06</v>
+        <v>2.474621359198665e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.087414890161704e-06</v>
+        <v>2.85791691180724e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.714133901816907e-06</v>
+        <v>2.486302094180859e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.749006905691868e-06</v>
+        <v>2.488082057227181e-06</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.736071602688493e-06</v>
+        <v>2.505923648986837e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.765016485869928e-06</v>
+        <v>2.541452058363407e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.80025299048121e-06</v>
+        <v>2.530265982347491e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.494161997553973e-06</v>
+        <v>2.389674396133858e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.688252087425541e-06</v>
+        <v>2.467715347544737e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.909557713580299e-06</v>
+        <v>2.600204975402078e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.763581428499654e-06</v>
+        <v>2.507676168370936e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.77689725560361e-06</v>
+        <v>2.52099217369445e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.794368283467061e-06</v>
+        <v>2.530450347188782e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.841878713560648e-06</v>
+        <v>2.550305532816661e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.811769164416117e-06</v>
+        <v>2.523809330843664e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.85436350843328e-06</v>
+        <v>2.552202315809413e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.694080198176592e-06</v>
+        <v>2.478386878202283e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.364324062810463e-06</v>
+        <v>4.146219231054447e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.674774897771707e-06</v>
+        <v>2.464275188813147e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.733869522352434e-06</v>
+        <v>2.494863573125099e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.752077510963123e-06</v>
+        <v>2.507430706827782e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.703148745338707e-06</v>
+        <v>2.478205635452814e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.737756418126965e-06</v>
+        <v>2.495070448613232e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.335936733080471e-06</v>
+        <v>3.082345860405626e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.74445045703619e-06</v>
+        <v>2.499933575335706e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.601849095022817e-06</v>
+        <v>3.288729968153428e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.700147133108632e-06</v>
+        <v>2.46987232931197e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.778280448462521e-06</v>
+        <v>2.533033652514585e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.129979821873581e-06</v>
+        <v>2.890692913181487e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.774213414107226e-06</v>
+        <v>2.529705953533644e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.784691842254842e-06</v>
+        <v>2.520520136010378e-06</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.607782909424766e-06</v>
+        <v>2.410200547027848e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.653387336100578e-06</v>
+        <v>2.45941830261667e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.622857312454202e-06</v>
+        <v>2.421190908724789e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.34034061538196e-06</v>
+        <v>2.297528878909682e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.589361051318674e-06</v>
+        <v>2.393304508129415e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.646197610150716e-06</v>
+        <v>2.426516230823973e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.594715433475377e-06</v>
+        <v>2.398299321015845e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.592024513146847e-06</v>
+        <v>2.399393883019514e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.61622606836532e-06</v>
+        <v>2.41143763101616e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.659589235073515e-06</v>
+        <v>2.418064657183506e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.599591651427424e-06</v>
+        <v>2.402390694943643e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.657230844865292e-06</v>
+        <v>2.415951062091187e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.583398535919388e-06</v>
+        <v>2.398977751558109e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.182477081471982e-06</v>
+        <v>3.980547898489596e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.572889065543431e-06</v>
+        <v>2.396822848332331e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.598867115752598e-06</v>
+        <v>2.403113895461456e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.612498104069437e-06</v>
+        <v>2.413374135083244e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.61241755006019e-06</v>
+        <v>2.404746742099713e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.612071665263044e-06</v>
+        <v>2.412972299275754e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.12883910971103e-06</v>
+        <v>2.934244440869425e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.620156939761486e-06</v>
+        <v>2.40649916313184e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.213546323496989e-06</v>
+        <v>3.014208395443918e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.592200137314804e-06</v>
+        <v>2.401449225019564e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.601582911597571e-06</v>
+        <v>2.404874959609494e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.945229788776981e-06</v>
+        <v>2.754823626315588e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.592033804500338e-06</v>
+        <v>2.403498600045351e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63562841904098e-06</v>
+        <v>2.42078163338015e-06</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.663081151126842e-06</v>
+        <v>2.452307881930198e-06</v>
       </c>
       <c r="C33" t="n">
-        <v>2.719119782098371e-06</v>
+        <v>2.498304464565699e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>2.738240421484289e-06</v>
+        <v>2.486759037932673e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>2.390140012181379e-06</v>
+        <v>2.331949308969346e-06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.644483895760035e-06</v>
+        <v>2.4287706370402e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>2.679583879056876e-06</v>
+        <v>2.443164283748736e-06</v>
       </c>
       <c r="H33" t="n">
-        <v>2.637630331958768e-06</v>
+        <v>2.431209904435156e-06</v>
       </c>
       <c r="I33" t="n">
-        <v>2.713368873783056e-06</v>
+        <v>2.476910405128443e-06</v>
       </c>
       <c r="J33" t="n">
-        <v>2.674586566875647e-06</v>
+        <v>2.446449254448867e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>2.730745060821839e-06</v>
+        <v>2.461397358497631e-06</v>
       </c>
       <c r="L33" t="n">
-        <v>2.697736463674692e-06</v>
+        <v>2.453872527456744e-06</v>
       </c>
       <c r="M33" t="n">
-        <v>2.755093468904539e-06</v>
+        <v>2.476420624810661e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>2.629924266266065e-06</v>
+        <v>2.432810786727497e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.267872983357222e-06</v>
+        <v>4.057640787922121e-06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.613055916783703e-06</v>
+        <v>2.421517665657922e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.668728236616089e-06</v>
+        <v>2.441792015429003e-06</v>
       </c>
       <c r="R33" t="n">
-        <v>2.677774853088934e-06</v>
+        <v>2.456124148099479e-06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.669660675156767e-06</v>
+        <v>2.444985958757552e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>2.679891506243527e-06</v>
+        <v>2.455774260980823e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>3.233483206270244e-06</v>
+        <v>3.003215851995123e-06</v>
       </c>
       <c r="V33" t="n">
-        <v>2.682361384089743e-06</v>
+        <v>2.447376452908185e-06</v>
       </c>
       <c r="W33" t="n">
-        <v>3.301347943096462e-06</v>
+        <v>3.087942906101109e-06</v>
       </c>
       <c r="X33" t="n">
-        <v>2.64068311269529e-06</v>
+        <v>2.430896056127988e-06</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.623141975836493e-06</v>
+        <v>2.424490553886198e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.042807125347367e-06</v>
+        <v>2.822384814545031e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.672269035497583e-06</v>
+        <v>2.457973548040159e-06</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.686415665034435e-06</v>
+        <v>2.453521509901513e-06</v>
       </c>
     </row>
   </sheetData>
